--- a/data/submission/FILLIT_Hot_Leads.xlsx
+++ b/data/submission/FILLIT_Hot_Leads.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hot leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hot leads'!$A$1:$X$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hot leads'!$A$1:$W$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -472,19 +472,18 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="60" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -545,65 +544,60 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Direct no.</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Current supplier</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Current supplier</t>
+          <t>Consumption (as recorded)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Consumption (as recorded)</t>
+          <t>Est. litres / month</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Est. litres / month</t>
+          <t>Fleet / equipment</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Fleet / equipment</t>
+          <t>Pain points</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Pain points</t>
+          <t>Latest comments</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Latest comments</t>
+          <t>First visit</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>First visit</t>
+          <t>Last visit</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Last visit</t>
+          <t>Visits</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Visits</t>
+          <t>Lead source</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Lead source</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Mentions CAFU</t>
         </is>
@@ -663,36 +657,36 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>0561340397 (Personal Number)</t>
+          <t>info@rpgroup.ae</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>info@rpgroup.ae</t>
+          <t>Multiple 3rd party (Speedex, Kajur)</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Multiple 3rd party (Speedex, Kajur)</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
           <t>40,000 Gallons/Day at Al Ruwais site; 30,000-45,000 Gallons/Month at 2nd site (Sharjah &amp; Ajman)</t>
         </is>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>4542000</v>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>200 trucks, buses and 250 generators</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Two site locations - 1) Al Ruwais 2) Sharjah &amp; Ajman. 30 camps. Current supplier: multiple 3rd party (Speedex, Kajur). Ask for credit basis.</t>
+        </is>
+      </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Two site locations - 1) Al Ruwais 2) Sharjah &amp; Ajman. 30 camps. Current supplier: multiple 3rd party (Speedex, Kajur). Ask for credit basis.</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -700,25 +694,20 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="n">
+      <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Merint Interior</t>
+          <t>Saif Al Saleh Transport LLC</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -739,80 +728,91 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Dubai Industrial City</t>
+          <t>Warsan / International City</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Building and civil contracting</t>
+          <t>Marine, boats and shipping</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>DIC (Dubai Industrial City)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>P.O Box #: 60219, England Cluster, International City</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Rishad (Procurement Manager)</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+          <t>Fayaiz</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>589139188</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>565474231</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>info@sastransportuae.com</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Welcome diesel, yes diesel trading</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>ENOC (chip)</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>50,000 L/month</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>50000</v>
+          <t>20000 G/Month+</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>75700</v>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>70+</t>
+        </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>50 trucks, 100 cars</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr"/>
+          <t>Price senstitive</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Price sensitive (Willing to switch if he get better price)</t>
+        </is>
+      </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>Runs 24 hours</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="n">
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Self-generated</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Sun Metal Casting Factory</t>
+          <t>Merint Interior</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -833,97 +833,75 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Sharjah Industrial Areas</t>
+          <t>Dubai Industrial City</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Metal, steel and aluminium</t>
+          <t>Building and civil contracting</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Office Floor -3, Al Raha Tower,
-Al Khan Corniche St - Sharjah</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Sharjah</t>
-        </is>
-      </c>
+          <t>DIC (Dubai Industrial City)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Clarence - Purchase Manager</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>+971 55 902 0311/+971 52 252 1047</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>522478874</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>Rishad (Procurement Manager)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>ENOC (chip)</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Third party</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2000G/Week</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>32778</v>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>18 Forklifts, 3 Passenger vans, 4 Trailers, 2 Burners</t>
-        </is>
-      </c>
+          <t>50,000 L/month</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>50 trucks, 100 cars</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>ENOC and ADNOC Price is high</t>
+          <t>Runs 24 hours</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>ADNOC is hard to get contract, enquired about freezone delivery - Hamriya, faced problems with CAFU, Asked for delivery charges, Looking for bulk rate and better than ADNOC price, Due to war consumption has reduced to half</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Al Fanous Al Fadhi Glass &amp; Aluminium Cont LLC</t>
+          <t>Poorav Chemical Transport</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -933,7 +911,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -941,95 +919,94 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Al Sajaa, Sharjah</t>
+          <t>Warsan / International City</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Metal, steel and aluminium</t>
+          <t>Marine, boats and shipping</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Al Sajaa Industrial Area, Sharjah, UAE (Dubai showroom in Al Quoz 2)</t>
+          <t>Warsan First, International City</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Taha</t>
+          <t>Ravikanth dubey</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>971 6 531 1421</t>
+          <t>567080969</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>507974845</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>info@pooravchemical.com</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Silver homes</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Fuel station</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>30000L/month+</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>30000</v>
+          <t>46,000L/Month</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>17 trucks</t>
+        </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>2trucks</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr"/>
+          <t>Price senstitive</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Wanted to contact sales for all the info on price and quotation</t>
+        </is>
+      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>Want to start immediately</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="n">
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Mgm General Contracting</t>
+          <t>Sun Metal Casting Factory</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1050,88 +1027,92 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Dubai (other)</t>
+          <t>Sharjah Industrial Areas</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Building and civil contracting</t>
+          <t>Metal, steel and aluminium</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3 43 St - Hor Al Anz - Dubai</t>
+          <t>Office Floor -3, Al Raha Tower,
+Al Khan Corniche St - Sharjah</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Dubai</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Clarence - Purchase Manager</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>04 266 7266</t>
+          <t>+971 55 902 0311/+971 52 252 1047</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Third party</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Maxwell fuel trading</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>5000l per week</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>21650</v>
+          <t>2000G/Week</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>32778</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>18 Forklifts, 3 Passenger vans, 4 Trailers, 2 Burners</t>
+        </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>machinery - 12, genertors - 10, vehichels - 15</t>
+          <t>ENOC and ADNOC Price is high</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>They take fuel in barrel for machinery. No discount for bulk.</t>
+          <t>ADNOC is hard to get contract, enquired about freezone delivery - Hamriya, faced problems with CAFU, Asked for delivery charges, Looking for bulk rate and better than ADNOC price, Due to war consumption has reduced to half</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>Hot Lead</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>1</v>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Bilal Industries L.L.C.</t>
+          <t>Al Fanous Al Fadhi Glass &amp; Aluminium Cont LLC</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1141,7 +1122,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1149,10 +1130,14 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Al Jurf, Ajman</t>
+          <t>Al Sajaa, Sharjah</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1162,86 +1147,73 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Al Jurf Ind. Area, Ajman, UAE (P.O. Box 13788)</t>
+          <t>Al Sajaa Industrial Area, Sharjah, UAE (Dubai showroom in Al Quoz 2)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Ghulam Mustafa (Accountant)</t>
+          <t>Taha</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>06 7487110 / 06 7480410</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>058 1285901</t>
-        </is>
-      </c>
+          <t>971 6 531 1421</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>accounts@bilalindustries.com</t>
+          <t>Fuel station</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Local vendor(Ajman)</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>4000-5000 G/month+</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>17032</v>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3 trucks, forklifts, 2 3T pickup</t>
-        </is>
-      </c>
+          <t>30000L/month+</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2trucks</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>Price sensitive</t>
+          <t>Want to start immediately</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>Asked for price and to send quote by email.</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="n">
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W7" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Menders Contracting And Maintenan</t>
+          <t>Mgm General Contracting</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1262,7 +1234,7 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Business Bay / Jumeirah / Barsha</t>
+          <t>Dubai (other)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1272,7 +1244,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Jumeirah 1 2nd of December street Jumeirah terrace building office 313</t>
+          <t>3 43 St - Hor Al Anz - Dubai</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1280,721 +1252,694 @@
           <t>Dubai</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>504910150</t>
-        </is>
-      </c>
+      <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>971 4 2255441</t>
+          <t>04 266 7266</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Harish - Procurement Manager</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>info@menders.ae</t>
+          <t>Maxwell fuel trading</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3rd party</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>4000 Gallons/ month</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>15140</v>
+          <t>5000l per week</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>21650</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>machinery - 12, genertors - 10, vehichels - 15</t>
+        </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>10 generators, 3 heavy machines and more other vechiles which not include trucks they outsource it</t>
+          <t>They take fuel in barrel for machinery. No discount for bulk.</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>overheating of generators</t>
+          <t>Hot Lead</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>Currently they get fuel delivered to site. Asked for credit</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="n">
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W8" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Bilal Industries L.L.C.</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Al Jurf, Ajman</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Metal, steel and aluminium</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Al Jurf Ind. Area, Ajman, UAE (P.O. Box 13788)</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Ajman</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Ghulam Mustafa (Accountant)</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>06 7487110 / 06 7480410</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>accounts@bilalindustries.com</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Local vendor(Ajman)</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4000-5000 G/month+</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>17032</v>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>3 trucks, forklifts, 2 3T pickup</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Price sensitive</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>Asked for price and to send quote by email.</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Menders Contracting And Maintenan</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Business Bay / Jumeirah / Barsha</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Building and civil contracting</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Jumeirah 1 2nd of December street Jumeirah terrace building office 313</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>504910150</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>971 4 2255441</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>info@menders.ae</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3rd party</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4000 Gallons/ month</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>15140</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>10 generators, 3 heavy machines and more other vechiles which not include trucks they outsource it</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>overheating of generators</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>Currently they get fuel delivered to site. Asked for credit</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>Fire Gates Safety &amp; Security System LLC</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Dubai Investment Park</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Other / unclassified</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Bayan Building, Dubai Investment Park 1, Dubai</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Dubai</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Ganesh</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>971 4 271 3794</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>569986040</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Royal Crown company (Al Quoz)</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2800galons /month</t>
         </is>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="O11" s="2" t="n">
         <v>10598</v>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>12 vehicles</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>Discounts and fuel quality</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>Purchase manager on leave.
 - Contacted POC over phone.
 - He wanted to contact sales team for all the information</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="V9" s="2" t="n">
+      <c r="U11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W9" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>BRIGHT SEASHORE SHIPPING LLC</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Dubai (other)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Marine, boats and shipping</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Mai Tower, Al Nahda 1, Dubai, U.A.E.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Dubai</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Atif</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>+971 4 236 2099</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>521812344</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3rd party (some Pakistani guy)</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>20000 AED/month +</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>5 heavy trucks</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>NO pain point</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>No issue from 3rd party</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>Self-generated</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>SHJ. CARBON FACTORY LLC</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Sharjah Industrial Areas</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Manufacturing and factory</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Industrial Area 3, Sharjah, UAE (Behind Caterpillar Showroom)</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Sharjah</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Sabu</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>971 6 542 0662</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>528312108</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Al Nasr diesel</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>2500L/month</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1trailer, 2 bulker, 4 forklifts</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle go to fuel stations to fill</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>They used to take from Cafu,but cafu stopped delivering</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="W11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>BRIGHT SEASHORE SHIPPING LLC</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Dubai (other)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Marine, boats and shipping</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Mai Tower, Al Nahda 1, Dubai, U.A.E.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Atif</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 236 2099</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3rd party (some Pakistani guy)</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>20000 AED/month +</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>5 heavy trucks</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>NO pain point</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>No issue from 3rd party</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SHJ. CARBON FACTORY LLC</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah Industrial Areas</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing and factory</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Industrial Area 3, Sharjah, UAE (Behind Caterpillar Showroom)</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Sabu</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>971 6 542 0662</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Al Nasr diesel</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2500L/month</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1trailer, 2 bulker, 4 forklifts</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle go to fuel stations to fill</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>They used to take from Cafu,but cafu stopped delivering</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Ismail Gheewala General Trading (L.L.C)</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Dubai Investment Park</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Manufacturing and factory</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Dubai Investment Park, Dubai, UAE</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Dubai</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Bikas (Manager)</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>971 4 399 9211</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>503612096</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>Procured from CAFU earlier. Currently procuring from other 3rd party</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>10000AED+ per month</t>
         </is>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="O14" s="2" t="n">
         <v>2500</v>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>5+ (1 bus, 1 forklift, 1 3ton truck, 1 6ton truck, 1 500L drum)</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>CAFU not coming to site.
 - 3rd suppliers have bad quality.
 - Extra charges</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>Very intrested so gave Sharukh sir's number</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="V12" s="2" t="n">
+      <c r="U14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W12" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Interstar Marbles Industries Llc</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Umm Al Quwain</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Building and civil contracting</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>near Sama Teeba for Food Industries-Branch 1 - Umm Al Thuoob - New Industrial Area - Emirate of Umm Al Quwain</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Umm Al Quwain</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Saji Mohanan</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>052 647 4970</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>65350300</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>info@interstarmarbles.ae</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>ADNOC(chip) &amp; local</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>7000 AED/month+</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>1750</v>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2 vehicles, 1 forklift</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Safeline Freight Forwarding LLC</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Dubai (other)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Transport, logistics and fleet</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>32A Street, Umm Ramool, Dubai, UAE</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Dubai</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Walid</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>971 600 590590 / +971 4 371 4427</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>ENOC, CAFU, other 3rd parties</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>1500L based on requirement</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>20(12 forklifts, 3 trucks, 1 crane, 4-5 other vehicles)</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>CAFU application is not working most of the times. Bad quality diesel from other 3rd parties. ADNOC not delivering small quantities.</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>Very intrested</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2003,7 +1948,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Uniforce Contracting Llc</t>
+          <t>Kadris Industries LLC</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2024,92 +1969,79 @@
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Dubai (other)</t>
+          <t>Dubai Industrial City</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Building and civil contracting</t>
+          <t>Manufacturing and factory</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25°14'19.6"N 55°18'18. - 6 Street 1 - Dubai</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Dubai</t>
-        </is>
-      </c>
+          <t>Saih Shuaib 3, P.O. Box 38054, Dubai Industrial City - Dubai</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>: 04 370 6944</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>+971 4 587 7127</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>sales@kadrisuae.com</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Al Quoz Diesel Trading, Siraj Diesel Trading</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Golden Power - ENOC</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>5000 AED for each vechile not for heavy vechiles, They have Generators which cost 15000 AED in a month</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>15 Vehichles and Few Generators</t>
-        </is>
-      </c>
+          <t>500 gallons/month, 18.9 dirham per gallon</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>1892</v>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Machines only</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Low quality fuel is reducing their vehicle's efficiency</t>
+          <t>Sensitive and inquiring about prices</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>They are buying from the third party and CAFU. they are buying petrol from CAFU and they are cost focused and enquired about extra charge and discounts</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X15" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="W15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Impact Metal Const Factory Llc</t>
+          <t>Interstar Marbles Industries Llc</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2130,96 +2062,83 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Sharjah Industrial Areas</t>
+          <t>Umm Al Quwain</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Metal, steel and aluminium</t>
+          <t>Building and civil contracting</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19895, City, Sharjah, Near National Paints, Sharjah, Industrial Area</t>
+          <t>near Sama Teeba for Food Industries-Branch 1 - Umm Al Thuoob - New Industrial Area - Emirate of Umm Al Quwain</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Umm Al Quwain</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Manoj</t>
+          <t>Saji Mohanan</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>+971-6-5350852</t>
+          <t>052 647 4970</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>555636014</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>info@interstarmarbles.ae</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>ADNOC(chip) &amp; local</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Nearest fuel station</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>2500AED/month+</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>625</v>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3 heavy pickups</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>CAFU has high charger</t>
-        </is>
-      </c>
+          <t>7000 AED/month+</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>1750</v>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2 vehicles, 1 forklift</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>Tried CAFU but left beacuse of charges</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="W16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>New city garage</t>
+          <t>Safeline Freight Forwarding LLC</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2240,76 +2159,91 @@
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Al Qusais</t>
+          <t>Dubai (other)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Auto workshop and equipment</t>
+          <t>Transport, logistics and fleet</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Haleb St - Al Qusais Industrial AreaAl - Al Qusais Ind. First - Dubai</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
+          <t>32A Street, Umm Ramool, Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>504987675</t>
+          <t>971 600 590590 / +971 4 371 4427</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>newcitygarge@gmail.com</t>
+          <t>ENOC, CAFU, other 3rd parties</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>ADNOC</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>500L per month</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
+          <t>1500L based on requirement</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>20(12 forklifts, 3 trucks, 1 crane, 4-5 other vehicles)</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>CAFU application is not working most of the times. Bad quality diesel from other 3rd parties. ADNOC not delivering small quantities.</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Very intrested</t>
+        </is>
+      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>needed awareness - focused on price and credit - has a good relationship with ADNOC dealer - long term relationship with transport companies - we handed over extra flyers</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="n">
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Technical Matalic Profiles Factory</t>
+          <t>Uniforce Contracting Llc</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2319,7 +2253,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2327,103 +2261,94 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Dubai (other)</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Building and civil contracting</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>25°14'19.6"N 55°18'18. - 6 Street 1 - Dubai</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>: 04 370 6944</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Golden Power - ENOC</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5000 AED for each vechile not for heavy vechiles, They have Generators which cost 15000 AED in a month</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>15 Vehichles and Few Generators</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Low quality fuel is reducing their vehicle's efficiency</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>They are buying from the third party and CAFU. they are buying petrol from CAFU and they are cost focused and enquired about extra charge and discounts</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Ajman Industrial Area</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Manufacturing and factory</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>New Industrial Area, Ajman</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Ajman</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Montaser</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>06 748 2220</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>586673593</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>info@tmpf.ae</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Fuel station</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>2000AED+(for forklifts only), based on operations for others</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>5(2 pickups, 1 trailor, 2 forklifts)</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>No trust on 3rd party suppliers</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>Very intrested (so gave Sharukh's sir number)</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Tamask building contracting</t>
+          <t>Impact Metal Const Factory Llc</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2444,68 +2369,91 @@
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Sharjah Industrial Areas</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Building and civil contracting</t>
+          <t>Metal, steel and aluminium</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>same address as MAJED HILAL CONTRACTING</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
+          <t>19895, City, Sharjah, Near National Paints, Sharjah, Industrial Area</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Manoj</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42599623</t>
+          <t>+971-6-5350852</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>50-60 gallons based on operations</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Nearest fuel station</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2500AED/month+</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>625</v>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>3 heavy pickups</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>CAFU has high charger</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Tried CAFU but left beacuse of charges</t>
+        </is>
+      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>use diesel mostly for generators</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="n">
-        <v>1</v>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X19" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Al Taj terminal service</t>
+          <t>New city garage</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2526,74 +2474,75 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Al Quoz</t>
+          <t>Al Qusais</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Food and beverage</t>
+          <t>Auto workshop and equipment</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Office#34, 3rd Floor - Al Quoz 4 - Dubai</t>
+          <t>Haleb St - Al Qusais Industrial AreaAl - Al Qusais Ind. First - Dubai</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43383511</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>504987675</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>newcitygarge@gmail.com</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>ADNOC</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>ADNOC</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>4-5 buses</t>
-        </is>
-      </c>
+          <t>500L per month</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>They go and fill from fuel station</t>
+          <t>needed awareness - focused on price and credit - has a good relationship with ADNOC dealer - long term relationship with transport companies - we handed over extra flyers</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>They go and fill from fuel station</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="n">
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Sharjah Carbon Factory</t>
+          <t>Technical Matalic Profiles Factory</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2603,7 +2552,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2611,10 +2560,14 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Sharjah Industrial Areas</t>
+          <t>Ajman Industrial Area</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2624,30 +2577,60 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Building # 13,Warehouse # 3,Industrial Area 3 - 3 29 St - Sharjah</t>
+          <t>New Industrial Area, Ajman</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Sharjah</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr"/>
+          <t>Ajman</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Montaser</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>06 542 0662</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
+          <t>06 748 2220</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>info@tmpf.ae</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Fuel station</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2000AED+(for forklifts only), based on operations for others</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>5(2 pickups, 1 trailor, 2 forklifts)</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>No trust on 3rd party suppliers</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Very intrested (so gave Sharukh's sir number)</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>Visited earlier (week 2)</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -2655,25 +2638,20 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
+      <c r="U21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Clear Ice LLC</t>
+          <t>Tamask building contracting</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2694,87 +2672,67 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Dubai Industrial City</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Food and beverage</t>
+          <t>Building and civil contracting</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Plot No: 531-895, Makani No: 03832 51558, Dubai Industrial City, Dubai-UAE</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Dubai</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Santhosh Valli
-- 2nd POC : Regan</t>
-        </is>
-      </c>
+          <t>same address as MAJED HILAL CONTRACTING</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>97148859490</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>48859490</t>
-        </is>
-      </c>
+          <t>42599623</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>ADNOC (chip)</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1 million AED/month</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n"/>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>Around 100 (pertol &amp; diesel)</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr"/>
+          <t>50-60 gallons based on operations</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>use diesel mostly for generators</t>
+        </is>
+      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>Asked for credit and petrol</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="n">
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CICON Building Materials (Steel Bar Fabrication)</t>
+          <t>Al Taj terminal service</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2795,74 +2753,73 @@
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Dubai Industrial City</t>
+          <t>Al Quoz</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Metal, steel and aluminium</t>
+          <t>Food and beverage</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>DIC (Dubai Industrial City)</t>
+          <t>Office#34, 3rd Floor - Al Quoz 4 - Dubai</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Durga</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>563449213</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>ADNOC (chip)</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>43383511</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>ADNOC</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>4-5 buses</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>100 trucks, 1 forklift</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr"/>
+          <t>They go and fill from fuel station</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>They go and fill from fuel station</t>
+        </is>
+      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>Abu Dhabi = main office; Dubai office on Sheikh Zayed Road</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="n">
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W23" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Self-generated</t>
         </is>
       </c>
-      <c r="X23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SCA Shipping Consultants</t>
+          <t>Sharjah Carbon Factory</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2883,82 +2840,418 @@
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
+          <t>Sharjah Industrial Areas</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing and factory</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Building # 13,Warehouse # 3,Industrial Area 3 - 3 29 St - Sharjah</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>06 542 0662</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>Visited earlier (week 2)</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Clear Ice LLC</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Dubai Industrial City</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Food and beverage</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Plot No: 531-895, Makani No: 03832 51558, Dubai Industrial City, Dubai-UAE</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Santhosh Valli
+- 2nd POC : Regan</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>97148859490</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>ADNOC (chip)</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1 million AED/month</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Around 100 (pertol &amp; diesel)</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>Asked for credit and petrol</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>CICON Building Materials (Steel Bar Fabrication)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Dubai Industrial City</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Metal, steel and aluminium</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>DIC (Dubai Industrial City)</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Durga</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>ADNOC (chip)</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>100 trucks, 1 forklift</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi = main office; Dubai office on Sheikh Zayed Road</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SCA Shipping Consultants</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>Business Bay / Jumeirah / Barsha</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Marine, boats and shipping</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Swiss tower, JLT</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Dubai</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Rinjit</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>r.lal@scagroup.net</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>ADNOC</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="n"/>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>12 generators</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>ADNOC has minimum quantity requirement</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>- Selling diesel to marine vehicles
 - Wants to procure for Fujairah location as well
 - Asked us to write a mail for more information and quotation info</t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr">
+      <c r="T27" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="V24" s="2" t="n">
+      <c r="U27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Self-generated</t>
         </is>
       </c>
-      <c r="X24" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Chinese Palace Group</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Business Bay / Jumeirah / Barsha</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Other / unclassified</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Office 2801, Floor 28, Building AA-1, Al Mazaya Business Avenue Building, JLT</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Sajad</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>30 vehicles</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>Need to send him details on WhatsApp</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X24"/>
+  <autoFilter ref="A1:W28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>